--- a/src/main/resources/espacios/english/1 - Vocabulary.xlsx
+++ b/src/main/resources/espacios/english/1 - Vocabulary.xlsx
@@ -5,11 +5,10 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="1 Shapes" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="117">
   <si>
     <t xml:space="preserve">Circle</t>
   </si>
@@ -176,29 +175,10 @@
     <t xml:space="preserve">ˈhɛksəˌɡɑn</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">Heptagon / </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="15"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Septagon</t>
-    </r>
+    <t xml:space="preserve">Heptagon / Septagon</t>
   </si>
   <si>
     <t xml:space="preserve">Heptágono / Septágono</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Heptagon / Septagon</t>
   </si>
   <si>
     <t xml:space="preserve">Octagon</t>
@@ -400,7 +380,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -427,11 +407,6 @@
       <name val="Arial"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="15"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -487,11 +462,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -518,9 +493,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1643400</xdr:colOff>
+      <xdr:colOff>1643040</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>1775160</xdr:rowOff>
+      <xdr:rowOff>1774800</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -533,8 +508,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="0"/>
-          <a:ext cx="1643400" cy="1775160"/>
+          <a:off x="12064320" y="0"/>
+          <a:ext cx="1643040" cy="1774800"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -556,9 +531,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1405800</xdr:colOff>
+      <xdr:colOff>1405440</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>1660680</xdr:rowOff>
+      <xdr:rowOff>1660320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -571,8 +546,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="1913760"/>
-          <a:ext cx="1405800" cy="1660680"/>
+          <a:off x="12064320" y="1913760"/>
+          <a:ext cx="1405440" cy="1660320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -594,9 +569,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1920600</xdr:colOff>
+      <xdr:colOff>1920240</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>2033280</xdr:rowOff>
+      <xdr:rowOff>2032920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -609,8 +584,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="3676680"/>
-          <a:ext cx="1920600" cy="2033280"/>
+          <a:off x="12064320" y="3676680"/>
+          <a:ext cx="1920240" cy="2032920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -632,9 +607,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1900800</xdr:colOff>
+      <xdr:colOff>1900440</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>1702080</xdr:rowOff>
+      <xdr:rowOff>1701720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -647,8 +622,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="5893920"/>
-          <a:ext cx="1900800" cy="1702080"/>
+          <a:off x="12064320" y="5893920"/>
+          <a:ext cx="1900440" cy="1701720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -670,9 +645,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1881000</xdr:colOff>
+      <xdr:colOff>1880640</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>2338560</xdr:rowOff>
+      <xdr:rowOff>2338200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -685,8 +660,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="7694280"/>
-          <a:ext cx="1881000" cy="2338560"/>
+          <a:off x="12064320" y="7694280"/>
+          <a:ext cx="1880640" cy="2338200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -708,9 +683,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1920600</xdr:colOff>
+      <xdr:colOff>1920240</xdr:colOff>
       <xdr:row>5</xdr:row>
-      <xdr:rowOff>2214720</xdr:rowOff>
+      <xdr:rowOff>2214360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -723,8 +698,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="10177200"/>
-          <a:ext cx="1920600" cy="2214720"/>
+          <a:off x="12064320" y="10177200"/>
+          <a:ext cx="1920240" cy="2214360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -746,9 +721,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1920600</xdr:colOff>
+      <xdr:colOff>1920240</xdr:colOff>
       <xdr:row>6</xdr:row>
-      <xdr:rowOff>1719720</xdr:rowOff>
+      <xdr:rowOff>1719360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -761,8 +736,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="12584520"/>
-          <a:ext cx="1920600" cy="1719720"/>
+          <a:off x="12064320" y="12584520"/>
+          <a:ext cx="1920240" cy="1719360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -784,9 +759,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1980000</xdr:colOff>
+      <xdr:colOff>1979640</xdr:colOff>
       <xdr:row>7</xdr:row>
-      <xdr:rowOff>1701720</xdr:rowOff>
+      <xdr:rowOff>1701360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -799,8 +774,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="14479920"/>
-          <a:ext cx="1980000" cy="1701720"/>
+          <a:off x="12064320" y="14479920"/>
+          <a:ext cx="1979640" cy="1701360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -822,9 +797,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1999800</xdr:colOff>
+      <xdr:colOff>1999440</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>2181600</xdr:rowOff>
+      <xdr:rowOff>2181240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -837,8 +812,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="16318080"/>
-          <a:ext cx="1999800" cy="2181600"/>
+          <a:off x="12064320" y="16318080"/>
+          <a:ext cx="1999440" cy="2181240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -860,9 +835,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2082960</xdr:colOff>
+      <xdr:colOff>2082600</xdr:colOff>
       <xdr:row>9</xdr:row>
-      <xdr:rowOff>1783080</xdr:rowOff>
+      <xdr:rowOff>1782720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -875,8 +850,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="18706320"/>
-          <a:ext cx="2082960" cy="1783080"/>
+          <a:off x="12064320" y="18706320"/>
+          <a:ext cx="2082600" cy="1782720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -898,9 +873,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2019600</xdr:colOff>
+      <xdr:colOff>2019240</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>1310760</xdr:rowOff>
+      <xdr:rowOff>1310400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -913,8 +888,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="20696400"/>
-          <a:ext cx="2019600" cy="1310760"/>
+          <a:off x="12064320" y="20696400"/>
+          <a:ext cx="2019240" cy="1310400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -936,9 +911,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1980000</xdr:colOff>
+      <xdr:colOff>1979640</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>1844280</xdr:rowOff>
+      <xdr:rowOff>1843920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -951,8 +926,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="22136760"/>
-          <a:ext cx="1980000" cy="1844280"/>
+          <a:off x="12064320" y="22136760"/>
+          <a:ext cx="1979640" cy="1843920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -974,9 +949,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2009520</xdr:colOff>
+      <xdr:colOff>2009160</xdr:colOff>
       <xdr:row>12</xdr:row>
-      <xdr:rowOff>1509480</xdr:rowOff>
+      <xdr:rowOff>1509120</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -989,8 +964,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="24088680"/>
-          <a:ext cx="2009520" cy="1509480"/>
+          <a:off x="12064320" y="24088680"/>
+          <a:ext cx="2009160" cy="1509120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1012,9 +987,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2019600</xdr:colOff>
+      <xdr:colOff>2019240</xdr:colOff>
       <xdr:row>13</xdr:row>
-      <xdr:rowOff>1857600</xdr:rowOff>
+      <xdr:rowOff>1857240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1027,8 +1002,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="25851600"/>
-          <a:ext cx="2019600" cy="1857600"/>
+          <a:off x="12064320" y="25851600"/>
+          <a:ext cx="2019240" cy="1857240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1050,9 +1025,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>1999800</xdr:colOff>
+      <xdr:colOff>1999440</xdr:colOff>
       <xdr:row>14</xdr:row>
-      <xdr:rowOff>2179080</xdr:rowOff>
+      <xdr:rowOff>2178720</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1065,8 +1040,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="27879840"/>
-          <a:ext cx="1999800" cy="2179080"/>
+          <a:off x="12064320" y="27879840"/>
+          <a:ext cx="1999440" cy="2178720"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1088,9 +1063,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2078640</xdr:colOff>
+      <xdr:colOff>2078280</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>2220120</xdr:rowOff>
+      <xdr:rowOff>2219760</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1103,8 +1078,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="30268080"/>
-          <a:ext cx="2078640" cy="2220120"/>
+          <a:off x="12064320" y="30268080"/>
+          <a:ext cx="2078280" cy="2219760"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1126,9 +1101,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2098440</xdr:colOff>
+      <xdr:colOff>2098080</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>2399040</xdr:rowOff>
+      <xdr:rowOff>2398680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1141,8 +1116,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="32656320"/>
-          <a:ext cx="2098440" cy="2399040"/>
+          <a:off x="12064320" y="32656320"/>
+          <a:ext cx="2098080" cy="2398680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1164,9 +1139,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2112480</xdr:colOff>
+      <xdr:colOff>2112120</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>2235240</xdr:rowOff>
+      <xdr:rowOff>2234880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1179,8 +1154,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="35271720"/>
-          <a:ext cx="2112480" cy="2235240"/>
+          <a:off x="12064320" y="35271720"/>
+          <a:ext cx="2112120" cy="2234880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1202,9 +1177,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2138040</xdr:colOff>
+      <xdr:colOff>2137680</xdr:colOff>
       <xdr:row>18</xdr:row>
-      <xdr:rowOff>2919600</xdr:rowOff>
+      <xdr:rowOff>2919240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1217,8 +1192,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="37697400"/>
-          <a:ext cx="2138040" cy="2919600"/>
+          <a:off x="12064320" y="37697400"/>
+          <a:ext cx="2137680" cy="2919240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1240,9 +1215,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2118240</xdr:colOff>
+      <xdr:colOff>2117880</xdr:colOff>
       <xdr:row>19</xdr:row>
-      <xdr:rowOff>2500200</xdr:rowOff>
+      <xdr:rowOff>2499840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1255,8 +1230,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="40824720"/>
-          <a:ext cx="2118240" cy="2500200"/>
+          <a:off x="12064320" y="40824720"/>
+          <a:ext cx="2117880" cy="2499840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1278,9 +1253,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2118240</xdr:colOff>
+      <xdr:colOff>2117880</xdr:colOff>
       <xdr:row>20</xdr:row>
-      <xdr:rowOff>2577960</xdr:rowOff>
+      <xdr:rowOff>2577600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1293,8 +1268,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="43534800"/>
-          <a:ext cx="2118240" cy="2577960"/>
+          <a:off x="12064320" y="43534800"/>
+          <a:ext cx="2117880" cy="2577600"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1316,9 +1291,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2118240</xdr:colOff>
+      <xdr:colOff>2117880</xdr:colOff>
       <xdr:row>21</xdr:row>
-      <xdr:rowOff>2629800</xdr:rowOff>
+      <xdr:rowOff>2629440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1331,8 +1306,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="46264320"/>
-          <a:ext cx="2118240" cy="2629800"/>
+          <a:off x="12064320" y="46264320"/>
+          <a:ext cx="2117880" cy="2629440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1354,9 +1329,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2098440</xdr:colOff>
+      <xdr:colOff>2098080</xdr:colOff>
       <xdr:row>22</xdr:row>
-      <xdr:rowOff>2412720</xdr:rowOff>
+      <xdr:rowOff>2412360</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1369,8 +1344,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="49126320"/>
-          <a:ext cx="2098440" cy="2412720"/>
+          <a:off x="12064320" y="49126320"/>
+          <a:ext cx="2098080" cy="2412360"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1392,9 +1367,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2244600</xdr:colOff>
+      <xdr:colOff>2244240</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>2623320</xdr:rowOff>
+      <xdr:rowOff>2622960</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1407,8 +1382,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="51741720"/>
-          <a:ext cx="2244600" cy="2623320"/>
+          <a:off x="12064320" y="51741720"/>
+          <a:ext cx="2244240" cy="2622960"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1430,9 +1405,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2316240</xdr:colOff>
+      <xdr:colOff>2315880</xdr:colOff>
       <xdr:row>24</xdr:row>
-      <xdr:rowOff>2107800</xdr:rowOff>
+      <xdr:rowOff>2107440</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1445,8 +1420,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="54565560"/>
-          <a:ext cx="2316240" cy="2107800"/>
+          <a:off x="12064320" y="54565560"/>
+          <a:ext cx="2315880" cy="2107440"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1468,9 +1443,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2415240</xdr:colOff>
+      <xdr:colOff>2414880</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>2392920</xdr:rowOff>
+      <xdr:rowOff>2392560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1483,8 +1458,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="56840040"/>
-          <a:ext cx="2415240" cy="2392920"/>
+          <a:off x="12064320" y="56840040"/>
+          <a:ext cx="2414880" cy="2392560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1506,9 +1481,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2435040</xdr:colOff>
+      <xdr:colOff>2434680</xdr:colOff>
       <xdr:row>26</xdr:row>
-      <xdr:rowOff>2478240</xdr:rowOff>
+      <xdr:rowOff>2477880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1521,8 +1496,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="59455800"/>
-          <a:ext cx="2435040" cy="2478240"/>
+          <a:off x="12064320" y="59455800"/>
+          <a:ext cx="2434680" cy="2477880"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1544,9 +1519,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2435040</xdr:colOff>
+      <xdr:colOff>2434680</xdr:colOff>
       <xdr:row>27</xdr:row>
-      <xdr:rowOff>2792880</xdr:rowOff>
+      <xdr:rowOff>2792520</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1559,8 +1534,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="62052120"/>
-          <a:ext cx="2435040" cy="2792880"/>
+          <a:off x="12064320" y="62052120"/>
+          <a:ext cx="2434680" cy="2792520"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1582,9 +1557,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2454840</xdr:colOff>
+      <xdr:colOff>2454480</xdr:colOff>
       <xdr:row>28</xdr:row>
-      <xdr:rowOff>2815560</xdr:rowOff>
+      <xdr:rowOff>2815200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1597,8 +1572,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="65066040"/>
-          <a:ext cx="2454840" cy="2815560"/>
+          <a:off x="12064320" y="65066040"/>
+          <a:ext cx="2454480" cy="2815200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1620,9 +1595,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2442600</xdr:colOff>
+      <xdr:colOff>2442240</xdr:colOff>
       <xdr:row>29</xdr:row>
-      <xdr:rowOff>2547000</xdr:rowOff>
+      <xdr:rowOff>2546640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1635,8 +1610,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="68041440"/>
-          <a:ext cx="2442600" cy="2547000"/>
+          <a:off x="12064320" y="68041440"/>
+          <a:ext cx="2442240" cy="2546640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1658,9 +1633,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2454840</xdr:colOff>
+      <xdr:colOff>2454480</xdr:colOff>
       <xdr:row>30</xdr:row>
-      <xdr:rowOff>2681280</xdr:rowOff>
+      <xdr:rowOff>2680920</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1673,8 +1648,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="70732800"/>
-          <a:ext cx="2454840" cy="2681280"/>
+          <a:off x="12064320" y="70732800"/>
+          <a:ext cx="2454480" cy="2680920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1696,9 +1671,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2494440</xdr:colOff>
+      <xdr:colOff>2494080</xdr:colOff>
       <xdr:row>31</xdr:row>
-      <xdr:rowOff>2835360</xdr:rowOff>
+      <xdr:rowOff>2835000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1711,8 +1686,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="73632600"/>
-          <a:ext cx="2494440" cy="2835360"/>
+          <a:off x="12064320" y="73632600"/>
+          <a:ext cx="2494080" cy="2835000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1734,9 +1709,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2573640</xdr:colOff>
+      <xdr:colOff>2573280</xdr:colOff>
       <xdr:row>32</xdr:row>
-      <xdr:rowOff>3470760</xdr:rowOff>
+      <xdr:rowOff>3470400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1749,8 +1724,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="76683960"/>
-          <a:ext cx="2573640" cy="3470760"/>
+          <a:off x="12064320" y="76683960"/>
+          <a:ext cx="2573280" cy="3470400"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1772,9 +1747,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2583720</xdr:colOff>
+      <xdr:colOff>2583360</xdr:colOff>
       <xdr:row>33</xdr:row>
-      <xdr:rowOff>2406600</xdr:rowOff>
+      <xdr:rowOff>2406240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1787,8 +1762,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="80342280"/>
-          <a:ext cx="2583720" cy="2406600"/>
+          <a:off x="12064320" y="80342280"/>
+          <a:ext cx="2583360" cy="2406240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1810,9 +1785,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2593440</xdr:colOff>
+      <xdr:colOff>2593080</xdr:colOff>
       <xdr:row>34</xdr:row>
-      <xdr:rowOff>2410200</xdr:rowOff>
+      <xdr:rowOff>2409840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1825,8 +1800,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="82957680"/>
-          <a:ext cx="2593440" cy="2410200"/>
+          <a:off x="12064320" y="82957680"/>
+          <a:ext cx="2593080" cy="2409840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1848,9 +1823,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2712240</xdr:colOff>
+      <xdr:colOff>2711880</xdr:colOff>
       <xdr:row>35</xdr:row>
-      <xdr:rowOff>2996640</xdr:rowOff>
+      <xdr:rowOff>2996280</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1863,8 +1838,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="85478760"/>
-          <a:ext cx="2712240" cy="2996640"/>
+          <a:off x="12064320" y="85478760"/>
+          <a:ext cx="2711880" cy="2996280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1886,9 +1861,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2732040</xdr:colOff>
+      <xdr:colOff>2731680</xdr:colOff>
       <xdr:row>36</xdr:row>
-      <xdr:rowOff>3865680</xdr:rowOff>
+      <xdr:rowOff>3865320</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1901,8 +1876,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="88681680"/>
-          <a:ext cx="2732040" cy="3865680"/>
+          <a:off x="12064320" y="88681680"/>
+          <a:ext cx="2731680" cy="3865320"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1924,9 +1899,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2732040</xdr:colOff>
+      <xdr:colOff>2731680</xdr:colOff>
       <xdr:row>37</xdr:row>
-      <xdr:rowOff>3756600</xdr:rowOff>
+      <xdr:rowOff>3756240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1939,8 +1914,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="92756520"/>
-          <a:ext cx="2732040" cy="3756600"/>
+          <a:off x="12064320" y="92756520"/>
+          <a:ext cx="2731680" cy="3756240"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1962,9 +1937,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2692440</xdr:colOff>
+      <xdr:colOff>2692080</xdr:colOff>
       <xdr:row>38</xdr:row>
-      <xdr:rowOff>3319200</xdr:rowOff>
+      <xdr:rowOff>3318840</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1977,8 +1952,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="96680160"/>
-          <a:ext cx="2692440" cy="3319200"/>
+          <a:off x="12064320" y="96680160"/>
+          <a:ext cx="2692080" cy="3318840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2000,9 +1975,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2712240</xdr:colOff>
+      <xdr:colOff>2711880</xdr:colOff>
       <xdr:row>39</xdr:row>
-      <xdr:rowOff>3310560</xdr:rowOff>
+      <xdr:rowOff>3310200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2015,8 +1990,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="100224720"/>
-          <a:ext cx="2712240" cy="3310560"/>
+          <a:off x="12064320" y="100224720"/>
+          <a:ext cx="2711880" cy="3310200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2038,9 +2013,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2732040</xdr:colOff>
+      <xdr:colOff>2731680</xdr:colOff>
       <xdr:row>40</xdr:row>
-      <xdr:rowOff>3092040</xdr:rowOff>
+      <xdr:rowOff>3091680</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2053,8 +2028,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="103673880"/>
-          <a:ext cx="2732040" cy="3092040"/>
+          <a:off x="12064320" y="103673880"/>
+          <a:ext cx="2731680" cy="3091680"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2076,9 +2051,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2771640</xdr:colOff>
+      <xdr:colOff>2771280</xdr:colOff>
       <xdr:row>41</xdr:row>
-      <xdr:rowOff>3348000</xdr:rowOff>
+      <xdr:rowOff>3347640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2091,8 +2066,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="106972200"/>
-          <a:ext cx="2771640" cy="3348000"/>
+          <a:off x="12064320" y="106972200"/>
+          <a:ext cx="2771280" cy="3347640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2114,9 +2089,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2831040</xdr:colOff>
+      <xdr:colOff>2830680</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>3472560</xdr:rowOff>
+      <xdr:rowOff>3472200</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2129,8 +2104,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="110478600"/>
-          <a:ext cx="2831040" cy="3472560"/>
+          <a:off x="12064320" y="110478600"/>
+          <a:ext cx="2830680" cy="3472200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2152,9 +2127,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>2870640</xdr:colOff>
+      <xdr:colOff>2870280</xdr:colOff>
       <xdr:row>43</xdr:row>
-      <xdr:rowOff>3195000</xdr:rowOff>
+      <xdr:rowOff>3194640</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -2167,8 +2142,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="12065040" y="114174360"/>
-          <a:ext cx="2870640" cy="3195000"/>
+          <a:off x="12064320" y="114174360"/>
+          <a:ext cx="2870280" cy="3194640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2298,7 +2273,7 @@
   <dimension ref="A1:D44"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="18.55" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.68"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="43.67"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="42.01"/>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="11.53"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="27.82"/>
@@ -2513,282 +2488,282 @@
         <v>52</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="213.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="1" t="s">
+      <c r="D20" s="1" t="s">
         <v>55</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="214.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="B21" s="1" t="s">
-        <v>58</v>
-      </c>
       <c r="D21" s="1" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="225.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="B22" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="B22" s="1" t="s">
-        <v>60</v>
-      </c>
       <c r="D22" s="1" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="205.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="B23" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="B23" s="1" t="s">
-        <v>62</v>
-      </c>
       <c r="D23" s="1" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="222.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B24" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="B24" s="1" t="s">
-        <v>64</v>
-      </c>
       <c r="D24" s="1" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="179.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="B25" s="1" t="s">
+      <c r="D25" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="205.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B26" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="B26" s="1" t="s">
+      <c r="D26" s="1" t="s">
         <v>69</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="204.45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="B27" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>72</v>
-      </c>
       <c r="D27" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="237.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B28" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="B28" s="1" t="s">
-        <v>74</v>
-      </c>
       <c r="D28" s="1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="234.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="B29" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="B29" s="1" t="s">
+      <c r="D29" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>77</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="211.9" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="B30" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="B30" s="1" t="s">
+      <c r="D30" s="1" t="s">
         <v>79</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="228.35" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B31" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B31" s="1" t="s">
+      <c r="D31" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>83</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="240.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B32" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="B32" s="1" t="s">
+      <c r="D32" s="1" t="s">
         <v>85</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="288.05" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B33" s="1" t="s">
         <v>87</v>
       </c>
-      <c r="B33" s="1" t="s">
+      <c r="D33" s="1" t="s">
         <v>88</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="205.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B34" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="B34" s="1" t="s">
+      <c r="D34" s="1" t="s">
         <v>91</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="198.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B35" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="D35" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="252.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B36" s="1" t="s">
         <v>96</v>
       </c>
-      <c r="B36" s="1" t="s">
+      <c r="D36" s="1" t="s">
         <v>97</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="320.85" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B37" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="B37" s="1" t="s">
+      <c r="D37" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="308.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="B38" s="1" t="s">
         <v>102</v>
       </c>
-      <c r="B38" s="1" t="s">
-        <v>103</v>
-      </c>
       <c r="D38" s="1" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="279.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="B39" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="B39" s="1" t="s">
-        <v>105</v>
-      </c>
       <c r="D39" s="1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="271.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="B40" s="1" t="s">
         <v>106</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="D40" s="1" t="s">
         <v>107</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="259.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="B41" s="1" t="s">
         <v>109</v>
       </c>
-      <c r="B41" s="1" t="s">
+      <c r="D41" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="276.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B42" s="1" t="s">
         <v>112</v>
       </c>
-      <c r="B42" s="1" t="s">
-        <v>113</v>
-      </c>
       <c r="D42" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="291" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="B43" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="B43" s="1" t="s">
-        <v>115</v>
-      </c>
       <c r="D43" s="1" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="267.15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="B44" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B44" s="1" t="s">
-        <v>117</v>
-      </c>
       <c r="D44" s="1" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
   </sheetData>
@@ -2801,25 +2776,4 @@
   </headerFooter>
   <drawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="2" width="11.53"/>
-  </cols>
-  <sheetData/>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>